--- a/output/Air_Quality.xlsx
+++ b/output/Air_Quality.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -506,6 +506,70 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G3" t="n">
+        <v>499</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:49:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G4" t="n">
+        <v>499</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:52:06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Air_Quality.xlsx
+++ b/output/Air_Quality.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -570,6 +570,38 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G5" t="n">
+        <v>499</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:26:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Air_Quality.xlsx
+++ b/output/Air_Quality.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -506,6 +506,198 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G3" t="n">
+        <v>499</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:09:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Malaka</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2828</v>
+      </c>
+      <c r="G4" t="n">
+        <v>464</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:11:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Malaka</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2828</v>
+      </c>
+      <c r="G5" t="n">
+        <v>464</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:12:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Johor Bahru</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>843</v>
+      </c>
+      <c r="G6" t="n">
+        <v>509</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:15:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kangar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>297</v>
+      </c>
+      <c r="G7" t="n">
+        <v>473</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:34:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kulai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>316</v>
+      </c>
+      <c r="G8" t="n">
+        <v>516</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:36:17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Air_Quality.xlsx
+++ b/output/Air_Quality.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -762,6 +762,70 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>164</v>
+      </c>
+      <c r="G11" t="n">
+        <v>453</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:39:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kulai</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>316</v>
+      </c>
+      <c r="G12" t="n">
+        <v>516</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:40:21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
